--- a/ead-ccs-test/data/CCS-Field-labels-and-filters.xlsx
+++ b/ead-ccs-test/data/CCS-Field-labels-and-filters.xlsx
@@ -5,19 +5,22 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimelbcloud.sharepoint.com/sites/OPGProjects/Initiatives/Cultural Collections Nexus/09 Cross Collection Search 2026 Delivery/06 Product Design Pod/02 Product Design/02 Working Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimelbcloud.sharepoint.com/sites/OPGProjects/Initiatives/Cultural Collections Nexus/09 Cross Collection Search 2026 Delivery/06 Product Design Pod/02 Product Design/02 Working Documents/CCS Fields (display) and Filters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC625532-1745-44CA-9831-65E8EC90D55F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="156" documentId="8_{2B45B022-508A-4952-828D-B6E5229828D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B452242F-D820-45CF-B55B-E17C69E4A753}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17920" xr2:uid="{7E81937D-8799-4F94-A634-A3C622128AD4}"/>
+    <workbookView xWindow="-28920" yWindow="-1710" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{7E81937D-8799-4F94-A634-A3C622128AD4}"/>
   </bookViews>
   <sheets>
-    <sheet name="CCS Field labels" sheetId="1" r:id="rId1"/>
+    <sheet name="CCS Field labels - Updated" sheetId="5" r:id="rId1"/>
     <sheet name="CCS Filters" sheetId="2" r:id="rId2"/>
+    <sheet name="OLD - CCS Field labels" sheetId="1" r:id="rId3"/>
+    <sheet name="OLD - Transformation fields" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CCS Field labels'!$A$1:$I$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'OLD - CCS Field labels'!$A$1:$I$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CCS Field labels - Updated'!$A$1:$G$89</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -43,9 +46,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="183">
-  <si>
-    <t>#</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="267">
+  <si>
+    <t>Display Order</t>
   </si>
   <si>
     <t>Display Field</t>
@@ -57,22 +60,22 @@
     <t xml:space="preserve">Brief Description </t>
   </si>
   <si>
+    <t>Transformation required for display</t>
+  </si>
+  <si>
+    <t>Specifications for display in CCS</t>
+  </si>
+  <si>
+    <t>Examples</t>
+  </si>
+  <si>
+    <t>Comments for review</t>
+  </si>
+  <si>
     <t>Data Type Reference</t>
   </si>
   <si>
     <t>Source system</t>
-  </si>
-  <si>
-    <t>Transformation required for display</t>
-  </si>
-  <si>
-    <t>Specifications for display in CCS</t>
-  </si>
-  <si>
-    <t>Examples</t>
-  </si>
-  <si>
-    <t>Questions to Ant / Alli</t>
   </si>
   <si>
     <t>Title</t>
@@ -86,9 +89,6 @@
 Determination - Used for taxon records where title does not apply</t>
   </si>
   <si>
-    <t>CMS</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
@@ -99,22 +99,22 @@
     <t>N/a</t>
   </si>
   <si>
+    <t>CMS</t>
+  </si>
+  <si>
     <t xml:space="preserve">Object Type </t>
   </si>
   <si>
     <t>Broad type of collection asset represented by the record</t>
   </si>
   <si>
-    <t>??</t>
-  </si>
-  <si>
     <t>When any data is not available, it will be blank and label also does not appear</t>
   </si>
   <si>
     <t>Specimen, Archive, Publication</t>
   </si>
   <si>
-    <t>What is the data type for Object type?</t>
+    <t>Object type (attribute in document header)</t>
   </si>
   <si>
     <t>Date</t>
@@ -131,36 +131,105 @@
   </si>
   <si>
     <t>1 - If 'display value' is available, CCS will display as-is
-2 - If 'date collected' is available, CCS will display as-is</t>
+2 - If 'date collected' is available, CCS will display as-is
+3 - Only when year is available, the system will add month and year for search purposes
+4 - Use creator's life dates when asset dates are not available</t>
   </si>
   <si>
     <t xml:space="preserve"> c. 1920 
 Middle Ages or Ming Dynasty</t>
   </si>
   <si>
+    <t xml:space="preserve">1 - If 'display value' is available, CCS will display as-is
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> c. 1920; Middle Ages or Ming Dynasty</t>
+  </si>
+  <si>
+    <t>2 - If 'date collected' is available, CCS will display as-is</t>
+  </si>
+  <si>
+    <t>3 - Only when year is available, the system will add month and year for search purposes</t>
+  </si>
+  <si>
+    <t>When Date in CMS is - 1920
+CCS system date will be - 1 Jan 1920 - 31 Dec 1920</t>
+  </si>
+  <si>
+    <t>4 - Use creator's life dates when asset dates are not available</t>
+  </si>
+  <si>
+    <t>This might be misleading - It might work for artists but not for other objects such as re-prints etc. It is recommeded to leave it blank when the date is not known</t>
+  </si>
+  <si>
+    <t>5 - Dislay sequence on CCS page - Title in bold; object type in small font; Title (in small); date</t>
+  </si>
+  <si>
     <t>Creator</t>
   </si>
   <si>
-    <t>Person Name, DoB, DoD, Role - Cultural affiliation - Organisation Name</t>
+    <t xml:space="preserve"> Primary Creator; Primary Creator Role; Secondary Creator; Secondary Creator Role; Party Name; Party Type; Date of Birth; Date of Death; organisation name
+Skin Name; Language; Clan; Artist Location; Country; Father's Country; Grandmother's Country; Moiety; Mother's Country; Region; Totem; </t>
   </si>
   <si>
     <t>Person or organisation responsible for creating the asset, e.g., John Longstaff</t>
   </si>
   <si>
+    <t xml:space="preserve">1 - Creator can be person or organisation (which is association)
+</t>
+  </si>
+  <si>
     <t>Agent</t>
   </si>
   <si>
-    <t>1 - Creator can be person or organisation (which is association)
-2 - Values displayed in CCS will be as per the source system - display value
-3 - For person, the values displayed would be in this order - "Full name (Dob - DoD) [nationality] role"
-4 - For organisation, the values displayed would be in this order - "organisation name (estab. DoB, closed. DoD)"
-5 - If any of the values are not available, then CCS will just not display the data</t>
-  </si>
-  <si>
-    <t>For person, Rupert Bunny (29 September 1864 - 25 May 1947) [Australian] Artist
-For organisation - Harringtons Metallurigists Pty Ltd (estab. 1906, closed 2002)
-For organisation - Harringtons Metallurigists Pty Ltd (estab. 1906)
-For organisation - Harringtons Metallurigists Pty Ltd (closed 2002)</t>
+    <t>2 - Values displayed in CCS will be as per the source system - display value</t>
+  </si>
+  <si>
+    <t>3 - For person, the values displayed would be in this order - "Full name (Dob - DoD) [nationality] role"</t>
+  </si>
+  <si>
+    <t>Rupert Bunny (b. 29 September 1864 - d. 25 May 1947) [Australian] Artist</t>
+  </si>
+  <si>
+    <t>It should be - 
+Rupert Bunny (b. 29 September 1864 - d. 25 May 1947)</t>
+  </si>
+  <si>
+    <t>4 - For organisation, the values displayed would be in this order - "organisation name (estab. DoB, closed. DoD)"</t>
+  </si>
+  <si>
+    <t>Harringtons Metallurigists Pty Ltd (estab. 1906 - closed 2002)</t>
+  </si>
+  <si>
+    <t>5 - If any of the values are not available, then CCS will just not display the data</t>
+  </si>
+  <si>
+    <t>For organisation, when closed date is not available - 
+Harringtons Metallurigists Pty Ltd (estab. 1906)</t>
+  </si>
+  <si>
+    <t>For organisation, when established date is not available - 
+Harringtons Metallurigists Pty Ltd (closed 2002)</t>
+  </si>
+  <si>
+    <t>For person, when the role is not available - 
+Rupert Bunny (b. 29 September 1864 - d. 25 May 1947) [Australian]</t>
+  </si>
+  <si>
+    <t>For person, when the DoB is not available - 
+Rupert Bunny (d. 25 May 1947) [Australian]</t>
+  </si>
+  <si>
+    <t>For person, when DoD is not available - 
+Rupert Bunny (d. 25 May 1947) [Australian]</t>
+  </si>
+  <si>
+    <t>For person, when the nationality is not available - 
+Rupert Bunny (b. 29 September 1864 - d. 25 May 1947) Artist</t>
+  </si>
+  <si>
+    <t>Need an example of the string with Cultural affiliation</t>
   </si>
   <si>
     <t>Associated Entity</t>
@@ -176,24 +245,29 @@
 2 - When any data is not available, it will be blank and label also does not appear</t>
   </si>
   <si>
-    <t xml:space="preserve">What is the data type for Association? </t>
+    <t>Agent (Associated agents)</t>
   </si>
   <si>
     <t xml:space="preserve">Place </t>
   </si>
   <si>
-    <t>L1, L2, L3, L4, L5 of Place - Collection Site</t>
+    <t>L1, L2, L3, L4, L5 of Place - Collection Site, Place title</t>
   </si>
   <si>
     <t>Place where the asset was produced, e.g., Melbourne, Victoria, Australia</t>
   </si>
   <si>
+    <t>1 - Each availale value will be displayed with a comma
+2 - When any data is not available, it will be blank and label also does not appear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tbd - Place has "Value" - Emu has a Value for each level (up to 5) and Vernon shows concatenated levels (in the Value field but a single instance)
+RG - There is also place title which  is useful for the users - eg: Old Quad Building </t>
+  </si>
+  <si>
     <t>Place</t>
   </si>
   <si>
-    <t>Is this always Display Value? I could not find any examples.</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
@@ -203,12 +277,12 @@
     <t>Descriptive or interpretive text about the asset</t>
   </si>
   <si>
+    <t>To display just the brief intro text (2-3 lines) - Need ux input</t>
+  </si>
+  <si>
     <t>Text</t>
   </si>
   <si>
-    <t>To display just the brief intro text (2-3 lines) - Need ux input</t>
-  </si>
-  <si>
     <t>Series</t>
   </si>
   <si>
@@ -227,7 +301,7 @@
     <t xml:space="preserve">Material </t>
   </si>
   <si>
-    <t>Material techniques, medium and extent (for archives)</t>
+    <t>Material techniques, medium</t>
   </si>
   <si>
     <t>Materials and/or techniques used, e.g., Oil on canvas</t>
@@ -236,33 +310,54 @@
     <t>Material technique &amp; Medium</t>
   </si>
   <si>
-    <t>Dimensions</t>
-  </si>
-  <si>
-    <t>Measures - Height, width, depth, diameter, weights, units, display value</t>
+    <t>Measurements (previosly mentioned as Dimensions)</t>
+  </si>
+  <si>
+    <t>Measures - Height, width, depth, diameter, weights, units, display value  and extent (Eg; archives)</t>
   </si>
   <si>
     <t>Physical or technical measurements</t>
   </si>
   <si>
-    <t>Measurement</t>
-  </si>
-  <si>
-    <t>1 - The information displayed on CCS will depend on the data available in source system
-2 - CCS label will be 'Dimensions (H x W x D)'
-3 - The value displayed will be whats available from source system.
-4 - Any available data needs to be displayed with the units (Units of measure)
-5 - The value displayed will have the details of the object along with the dimensions 
-6 - The information will be displayed as per the 'display value' when available (Example is MDHS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vase 180 x 30 x 100 cm
-Vase 180 cm
-Vase 180 x 30 cm
-Vase 180 x 100 cm
+    <t xml:space="preserve">1 - The information displayed on CCS will depend on the data available in source system
 </t>
   </si>
   <si>
+    <t>2 - CCS label will be 'Measurements'</t>
+  </si>
+  <si>
+    <t>3 - The value displayed will be whats available from source system.</t>
+  </si>
+  <si>
+    <t>When only one value is available - 
+Vase 180 cm</t>
+  </si>
+  <si>
+    <t>4 - Any available data needs to be displayed with the units (Units of measure)</t>
+  </si>
+  <si>
+    <t>When weight is not available - 
+Vase 180 x 30 x 100 cm 
+Extent - 2 boxes</t>
+  </si>
+  <si>
+    <t>TBD - The values for measurements are diverse and recorded unevenly cross Collections. 
+18.0 x 3.0 x 10.0 cm (vase)  - currenlty in MDHS
+These measurements be multiple values - one for box, one for contents - items identified in brackets
+Currently EMu and Vernon does H W D 
+We will review the data mapping (from Ant) and get uidance from Ux (Dean)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - The value displayed will have the details of the object along with the dimensions </t>
+  </si>
+  <si>
+    <t>Vase 180 x 30 x 100 cm 250 gms
+Extent - 2 boxes</t>
+  </si>
+  <si>
+    <t>6 - The information will be displayed as per the 'display value' when available (Example is MDHS)</t>
+  </si>
+  <si>
     <t>Inscription</t>
   </si>
   <si>
@@ -272,6 +367,19 @@
     <t>Inscription, signature, label or other text recorded on the asset</t>
   </si>
   <si>
+    <t>1 - Multiple inscriptions should be displayed by inscription type:
+2 - Each Inscription type will be identified by 'inscription type' and  list of inscriptions separated by comma
+3 - When any data is not available, it will be blank and label also does not appear</t>
+  </si>
+  <si>
+    <t>Signatures; signature 1, signature 2
+Inscriptions: inscription 1, inscription 2</t>
+  </si>
+  <si>
+    <t>MDHS has signatures, inscriptions etc - MDHS has two fields (free text and table) where this data is stored. CCS needs to map both and display as-is.
+FEIT has primary and secondary</t>
+  </si>
+  <si>
     <t>Language</t>
   </si>
   <si>
@@ -287,22 +395,19 @@
     <t>Affiliation</t>
   </si>
   <si>
-    <t>Is it just 'display value'?</t>
-  </si>
-  <si>
     <t>Accession Number</t>
   </si>
   <si>
     <t>Accession or catalogue number, e.g., 1987.0043</t>
-  </si>
-  <si>
-    <t>Identifier</t>
   </si>
   <si>
     <t>1 - Accession number displays as it is in source system(CMS)
 2 - This is mandatory data; CCS cannot display a record</t>
   </si>
   <si>
+    <t>Identifier</t>
+  </si>
+  <si>
     <t>Copyright</t>
   </si>
   <si>
@@ -342,30 +447,90 @@
     <t>Classification within a defined scheme, e.g., Furniture or Eucalyptus globulus</t>
   </si>
   <si>
+    <t>1 - Primary and Secondary classification, when available, will be in a string (one line of text).</t>
+  </si>
+  <si>
+    <t>&lt;primary classification&gt; - &lt;secondary classification&gt;</t>
+  </si>
+  <si>
     <t>Subject Classification</t>
   </si>
   <si>
+    <t>2 - Primary and Secondary Classification will be hyphenated to distinguish.</t>
+  </si>
+  <si>
+    <t>3 - It is preferred that these classifications work as a hyperlink - Clicking on this link will enable the user to search for records with the selected classification.</t>
+  </si>
+  <si>
+    <t>4 - When any data is not available, it will be blank and label also does not appear</t>
+  </si>
+  <si>
+    <t>&lt;secondary classification&gt;</t>
+  </si>
+  <si>
+    <t>5 - The user will not be informed if the value presented here is primary or secondary classification</t>
+  </si>
+  <si>
     <t>Subject</t>
   </si>
   <si>
     <t>Topic, theme or concept represented by the asset, e.g., Military history</t>
   </si>
   <si>
+    <t>1 - When any data is not available, it will be blank and label also does not appear</t>
+  </si>
+  <si>
+    <t>2 - It is preferred that these classifications work as a hyperlink - Clicking on this link will enable the user to search for records with the selected classification.</t>
+  </si>
+  <si>
     <t>Source URL</t>
   </si>
   <si>
     <t xml:space="preserve">Link to the asset in an existing or legacy collection browser. </t>
   </si>
   <si>
+    <t>1 - The availability of the external systems (browsers) is out of scope for CCS (broken urls, websites are down etc)</t>
+  </si>
+  <si>
+    <t>Examples of inconsistency and unavailability of browsers:
+1 - Malformed url supplied (e.g. htp:/example missing protocol, stray text)
+2 - URL points to a broken/non-existent page (404)
+3 - External site is unreachable/down</t>
+  </si>
+  <si>
+    <t>2 - When any data is not available, it will be blank and label also does not appear</t>
+  </si>
+  <si>
+    <t>Related Record</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - When multiple values, CCS will list each value in separate lines
+</t>
+  </si>
+  <si>
+    <t>Parent - related record 1; 
+Child - related record 3</t>
+  </si>
+  <si>
+    <t>2 - Each line will be identified with a relation type (parent or child)</t>
+  </si>
+  <si>
+    <t>3 - There will always be one parent record but multiple child records</t>
+  </si>
+  <si>
+    <t>1 - Confirm that there will always be one parent record and multiple child records 
+2 - Each child record will be presented in a separate line</t>
+  </si>
+  <si>
     <t>Related Parent Record</t>
   </si>
   <si>
+    <t>Remove</t>
+  </si>
+  <si>
     <t>Related Child Record</t>
   </si>
   <si>
-    <t>Related Record</t>
-  </si>
-  <si>
     <t>Licence Type</t>
   </si>
   <si>
@@ -388,6 +553,9 @@
   </si>
   <si>
     <t>Person or organisation responsible for creating the digital asset</t>
+  </si>
+  <si>
+    <t>#</t>
   </si>
   <si>
     <t>Filter Section Title​</t>
@@ -410,16 +578,13 @@
     <t>Filter type</t>
   </si>
   <si>
-    <t>Additional Functionality</t>
-  </si>
-  <si>
     <t>Filter options</t>
   </si>
   <si>
     <t>CCS Data model Ref</t>
   </si>
   <si>
-    <t>Questions to Alli and Ant</t>
+    <t>Comments</t>
   </si>
   <si>
     <t>Collection details​</t>
@@ -461,6 +626,9 @@
     <t>Agent - Creator</t>
   </si>
   <si>
+    <t>Creator role</t>
+  </si>
+  <si>
     <t>Creator Date of Birth​</t>
   </si>
   <si>
@@ -500,7 +668,7 @@
     <t>Date - Created Period</t>
   </si>
   <si>
-    <t>Is this a derived value that needs to be calculated?</t>
+    <t>This needs to be derived - Eg BCE vs CE</t>
   </si>
   <si>
     <t>Classification​</t>
@@ -509,7 +677,7 @@
     <t>List of all available classifications</t>
   </si>
   <si>
-    <t xml:space="preserve">Might need UI input </t>
+    <t>Need UI input - consider both primary and secondary</t>
   </si>
   <si>
     <t>Object Type​</t>
@@ -545,7 +713,7 @@
     <t>Place - Place of Production</t>
   </si>
   <si>
-    <t>Region? - Is this a derived data point from Place of production?</t>
+    <t>This can be just the string - place (field)</t>
   </si>
   <si>
     <t>Subject / Topic​</t>
@@ -554,7 +722,7 @@
     <t>Subject Terms​</t>
   </si>
   <si>
-    <t>List of all available subjetc terms</t>
+    <t>List of all available subject terms</t>
   </si>
   <si>
     <t>Subject Agent​</t>
@@ -563,12 +731,6 @@
     <t>Unsure</t>
   </si>
   <si>
-    <t>Subject &gt; Agent</t>
-  </si>
-  <si>
-    <t>Is this same as creator name? Do we need this?</t>
-  </si>
-  <si>
     <t>Subject Location​</t>
   </si>
   <si>
@@ -584,10 +746,10 @@
     <t>List of all available events?</t>
   </si>
   <si>
-    <t>Subject &gt; Event</t>
-  </si>
-  <si>
-    <t>Do we need this?</t>
+    <t xml:space="preserve">Subject </t>
+  </si>
+  <si>
+    <t>This is not mapped for EMu and it is part of 'subject'</t>
   </si>
   <si>
     <t>Copyright &amp; Advisory​</t>
@@ -627,13 +789,226 @@
   </si>
   <si>
     <t>Material Technique - Digital format</t>
+  </si>
+  <si>
+    <t>Open questions</t>
+  </si>
+  <si>
+    <t>Title (big) - Object type(small) - title (in small) - date</t>
+  </si>
+  <si>
+    <t>Person Name, DoB, DoD, Role - Cultural affiliation - Organisation Name</t>
+  </si>
+  <si>
+    <t>1 - Creator can be person or organisation (which is association)
+2 - Values displayed in CCS will be as per the source system - display value
+3 - For person, the values displayed would be in this order - "Full name (Dob - DoD) [nationality] role"
+4 - For organisation, the values displayed would be in this order - "organisation name (estab. DoB, closed. DoD)"
+5 - If any of the values are not available, then CCS will just not display the data</t>
+  </si>
+  <si>
+    <t>For person, Rupert Bunny (29 September 1864 - 25 May 1947) [Australian] Artist
+For organisation - Harringtons Metallurigists Pty Ltd (estab. 1906, closed 2002)
+For organisation - Harringtons Metallurigists Pty Ltd (estab. 1906)
+For organisation - Harringtons Metallurigists Pty Ltd (closed 2002)</t>
+  </si>
+  <si>
+    <t>L1, L2, L3, L4, L5 of Place - Collection Site</t>
+  </si>
+  <si>
+    <t>When any data is not available, it will be blank and label also does not appear
+Display each level with a comma</t>
+  </si>
+  <si>
+    <t>tbd - Place has "Value" - Emu has a Value for each level (up to 5) and Vernon shows concatenated levels (in the Value field but a single instance)
+RG - There is also place title which  is useful for the users - eg: Old Quad Building - RG will send examples</t>
+  </si>
+  <si>
+    <t>RG will send examples</t>
+  </si>
+  <si>
+    <t>Dimensions</t>
+  </si>
+  <si>
+    <t>Measurement</t>
+  </si>
+  <si>
+    <t>1 - The information displayed on CCS will depend on the data available in source system
+2 - CCS label will be 'Dimensions (H x W x D)'
+3 - The value displayed will be whats available from source system.
+4 - Any available data needs to be displayed with the units (Units of measure)
+5 - The value displayed will have the details of the object along with the dimensions 
+6 - The information will be displayed as per the 'display value' when available (Example is MDHS)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Vase 180 x 30 x 100 cm
+Vase 180 cm
+Vase 180 x 30 cm
+Vase 180 x 100 cm
+New ex:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Vase 180 x 30 x 100 cm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>250 gms
+Extent - 2 boxes</t>
+    </r>
+  </si>
+  <si>
+    <t>Add extent to dimensions and rename dimensions to measurements - Remove HxWxD
+Extent should be a new line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiple inscriptions are displayed by inscription type:
+Inscription type - list of inscriptions separated by comma
+</t>
+  </si>
+  <si>
+    <t>This is multiple values - JJ to check with Ant about skin name, country, artist location as an example</t>
+  </si>
+  <si>
+    <t>Primary and secondary classifications when available will be in a string and hyphenated - Verify the hyperlinks work</t>
+  </si>
+  <si>
+    <t>Hyperlinks here too</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="6" tint="-0.499984740745262"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Malformed url supplied (e.g. htp:/example missing protocol, stray text)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+URL points to a broken/non-existent page (404)
+External site is unreachable/down
+If so, how should the error message be displayed?</t>
+    </r>
+  </si>
+  <si>
+    <t>When any data is not available, it will be blank and label also does not appear
+When multiple values, CCS will list each value in separate lines
+Each line will be identified with a relation type (parent or child)</t>
+  </si>
+  <si>
+    <t>When Date in CMS is - 1920
+CCS system date will be - 1 jan 1920 - 31 Dec 1920</t>
+  </si>
+  <si>
+    <t>5 - Title in bold; object type in small font; Title (in small); dates</t>
+  </si>
+  <si>
+    <t>Not sure - perhaps a visual will help</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+</t>
+  </si>
+  <si>
+    <t>Rupert Bunny (29 September 1864 - 25 May 1947) [Australian] Artist</t>
+  </si>
+  <si>
+    <t>Harringtons Metallurigists Pty Ltd (estab. 1906, closed 2002)</t>
+  </si>
+  <si>
+    <t>For person, when the role is not available - 
+Rupert Bunny (29 September 1864 - 25 May 1947) [Australian]</t>
+  </si>
+  <si>
+    <t>For person, when the nationality is not available - 
+Rupert Bunny (29 September 1864 - 25 May 1947) Artist</t>
+  </si>
+  <si>
+    <t>Same as above</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Measurements
+</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Dimensions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Measures - Height, width, depth, diameter, weights, units, display value, extent</t>
+  </si>
+  <si>
+    <t>18.0 x 3.0 x 10.0 cm (vase)  - currenlty in MDHS
+These measurements be multiple values - one for box, one for contents - items identified in brackets
+Currently EMu and Vernon does H W D - check with Ant and Ux</t>
+  </si>
+  <si>
+    <t>Primary Classification; Secondary Classification</t>
+  </si>
+  <si>
+    <t>Classifications within a defined scheme, e.g., Furniture or Eucalyptus globulus</t>
+  </si>
+  <si>
+    <t>2 - Primary and Secondary Classification will be hyphemated to distinguish.</t>
+  </si>
+  <si>
+    <t>1 - When multiple values, CCS will list each value in separate lines
+2 - Each line will be identified with a relation type (parent or child)
+3 - When any data is not available, it will be blank and label also does not appear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will there be multiple parent and / or child records? If yes, can we display each in a separate line?
+</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -702,8 +1077,32 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="6" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -728,6 +1127,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -741,7 +1158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -760,9 +1177,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -785,14 +1199,77 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1127,25 +1604,1971 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76FB55C7-B5D8-4271-9CA2-C29C97B8B401}">
+  <dimension ref="A1:J116"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="8" style="4" customWidth="1"/>
+    <col min="2" max="2" width="16" style="4" customWidth="1"/>
+    <col min="3" max="3" width="21.75" style="4" customWidth="1"/>
+    <col min="4" max="4" width="35.75" style="4" customWidth="1"/>
+    <col min="5" max="5" width="34.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="53.25" style="4" customWidth="1"/>
+    <col min="7" max="7" width="49.5" style="4" customWidth="1"/>
+    <col min="8" max="8" width="46.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.5" style="4" customWidth="1"/>
+    <col min="10" max="10" width="15.25" style="4" customWidth="1"/>
+    <col min="11" max="16384" width="8.75" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="32.25">
+      <c r="A1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="106.5">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="26"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+    </row>
+    <row r="4" spans="1:10" ht="30.75">
+      <c r="A4" s="4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="26"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+    </row>
+    <row r="6" spans="1:10" ht="76.5">
+      <c r="A6" s="4">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="30.75">
+      <c r="F7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="F8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="30.75">
+      <c r="F9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="60.75">
+      <c r="F10" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="30.75">
+      <c r="F11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" s="14"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="26"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+    </row>
+    <row r="13" spans="1:10" ht="198">
+      <c r="A13" s="4">
+        <v>4</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="30.75">
+      <c r="F14" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="30.75">
+      <c r="F15" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H15" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="30.75">
+      <c r="F16" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H16" s="14"/>
+    </row>
+    <row r="17" spans="1:10" ht="30.75">
+      <c r="F17" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="30.75">
+      <c r="G18" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="45.75">
+      <c r="G19" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="30.75">
+      <c r="G20" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="30.75">
+      <c r="G21" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="30.75">
+      <c r="G22" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="G23" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="H23" s="14"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="26"/>
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="26"/>
+    </row>
+    <row r="25" spans="1:10" ht="45.75">
+      <c r="A25" s="4">
+        <v>5</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="26"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="26"/>
+    </row>
+    <row r="27" spans="1:10" ht="76.5">
+      <c r="A27" s="4">
+        <v>6</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H27" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="27"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="27"/>
+    </row>
+    <row r="29" spans="1:10" ht="30.75">
+      <c r="A29" s="4">
+        <v>7</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="26"/>
+      <c r="B30" s="26"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="26"/>
+      <c r="J30" s="26"/>
+    </row>
+    <row r="31" spans="1:10" ht="30.75">
+      <c r="A31" s="4">
+        <v>8</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="26"/>
+      <c r="B32" s="26"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="26"/>
+      <c r="J32" s="26"/>
+    </row>
+    <row r="33" spans="1:10" ht="30.75">
+      <c r="A33" s="4">
+        <v>9</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="26"/>
+      <c r="B34" s="26"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="26"/>
+      <c r="I34" s="26"/>
+      <c r="J34" s="26"/>
+    </row>
+    <row r="35" spans="1:10" ht="30.75">
+      <c r="A35" s="4">
+        <v>10</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="26"/>
+      <c r="B36" s="26"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="26"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="26"/>
+      <c r="J36" s="26"/>
+    </row>
+    <row r="37" spans="1:10" ht="60.75">
+      <c r="A37" s="4">
+        <v>11</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="F38" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="30.75">
+      <c r="F39" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="121.5">
+      <c r="F40" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H40" s="14" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="30.75">
+      <c r="F41" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="30.75">
+      <c r="F42" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="26"/>
+      <c r="B43" s="26"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="26"/>
+      <c r="H43" s="26"/>
+      <c r="I43" s="26"/>
+      <c r="J43" s="26"/>
+    </row>
+    <row r="44" spans="1:10" ht="76.5">
+      <c r="A44" s="4">
+        <v>12</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H44" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="26"/>
+      <c r="B45" s="26"/>
+      <c r="C45" s="26"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="26"/>
+      <c r="F45" s="26"/>
+      <c r="G45" s="26"/>
+      <c r="H45" s="26"/>
+      <c r="I45" s="26"/>
+      <c r="J45" s="26"/>
+    </row>
+    <row r="46" spans="1:10" ht="30.75">
+      <c r="A46" s="4">
+        <v>13</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="26"/>
+      <c r="B47" s="26"/>
+      <c r="C47" s="26"/>
+      <c r="D47" s="26"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="26"/>
+      <c r="G47" s="26"/>
+      <c r="H47" s="26"/>
+      <c r="I47" s="26"/>
+      <c r="J47" s="26"/>
+    </row>
+    <row r="48" spans="1:10" ht="30.75">
+      <c r="A48" s="4">
+        <v>14</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H48" s="14"/>
+      <c r="I48" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="26"/>
+      <c r="B49" s="26"/>
+      <c r="C49" s="26"/>
+      <c r="D49" s="26"/>
+      <c r="E49" s="26"/>
+      <c r="F49" s="26"/>
+      <c r="G49" s="26"/>
+      <c r="H49" s="27"/>
+      <c r="I49" s="26"/>
+      <c r="J49" s="26"/>
+    </row>
+    <row r="50" spans="1:10" ht="30.75">
+      <c r="A50" s="4">
+        <v>15</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="30.75">
+      <c r="F51" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" s="26"/>
+      <c r="B52" s="26"/>
+      <c r="C52" s="26"/>
+      <c r="D52" s="26"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="26"/>
+      <c r="G52" s="26"/>
+      <c r="H52" s="26"/>
+      <c r="I52" s="26"/>
+      <c r="J52" s="26"/>
+    </row>
+    <row r="53" spans="1:10" ht="30.75">
+      <c r="A53" s="4">
+        <v>16</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D53" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" s="26"/>
+      <c r="B54" s="26"/>
+      <c r="C54" s="26"/>
+      <c r="D54" s="30"/>
+      <c r="E54" s="26"/>
+      <c r="F54" s="26"/>
+      <c r="G54" s="26"/>
+      <c r="H54" s="26"/>
+      <c r="I54" s="26"/>
+      <c r="J54" s="26"/>
+    </row>
+    <row r="55" spans="1:10" ht="45.75">
+      <c r="A55" s="4">
+        <v>17</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="J55" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" s="26"/>
+      <c r="B56" s="26"/>
+      <c r="C56" s="26"/>
+      <c r="D56" s="26"/>
+      <c r="E56" s="26"/>
+      <c r="F56" s="26"/>
+      <c r="G56" s="26"/>
+      <c r="H56" s="26"/>
+      <c r="I56" s="26"/>
+      <c r="J56" s="26"/>
+    </row>
+    <row r="57" spans="1:10" ht="30.75">
+      <c r="A57" s="4">
+        <v>18</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" s="26"/>
+      <c r="B58" s="26"/>
+      <c r="C58" s="26"/>
+      <c r="D58" s="26"/>
+      <c r="E58" s="26"/>
+      <c r="F58" s="26"/>
+      <c r="G58" s="26"/>
+      <c r="H58" s="26"/>
+      <c r="I58" s="26"/>
+      <c r="J58" s="26"/>
+    </row>
+    <row r="59" spans="1:10" ht="30.75">
+      <c r="A59" s="4">
+        <v>19</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I59" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="J59" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" s="26"/>
+      <c r="B60" s="26"/>
+      <c r="C60" s="26"/>
+      <c r="D60" s="26"/>
+      <c r="E60" s="26"/>
+      <c r="F60" s="26"/>
+      <c r="G60" s="26"/>
+      <c r="H60" s="26"/>
+      <c r="I60" s="26"/>
+      <c r="J60" s="26"/>
+    </row>
+    <row r="61" spans="1:10" ht="30.75">
+      <c r="A61" s="4">
+        <v>20</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" s="26"/>
+      <c r="B62" s="26"/>
+      <c r="C62" s="26"/>
+      <c r="D62" s="26"/>
+      <c r="E62" s="26"/>
+      <c r="F62" s="26"/>
+      <c r="G62" s="26"/>
+      <c r="H62" s="26"/>
+      <c r="I62" s="26"/>
+      <c r="J62" s="26"/>
+    </row>
+    <row r="63" spans="1:10" ht="30.75">
+      <c r="A63" s="4">
+        <v>21</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I63" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J63" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="30.75">
+      <c r="F64" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="45.75">
+      <c r="F65" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G65" s="3"/>
+    </row>
+    <row r="66" spans="1:10" ht="30.75">
+      <c r="F66" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="30.75">
+      <c r="F67" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G67" s="3"/>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" s="26"/>
+      <c r="B68" s="26"/>
+      <c r="C68" s="26"/>
+      <c r="D68" s="26"/>
+      <c r="E68" s="26"/>
+      <c r="F68" s="26"/>
+      <c r="G68" s="26"/>
+      <c r="H68" s="26"/>
+      <c r="I68" s="26"/>
+      <c r="J68" s="26"/>
+    </row>
+    <row r="69" spans="1:10" ht="30.75">
+      <c r="A69" s="4">
+        <v>22</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="I69" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="J69" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="45.75">
+      <c r="F70" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71" s="26"/>
+      <c r="B71" s="26"/>
+      <c r="C71" s="26"/>
+      <c r="D71" s="26"/>
+      <c r="E71" s="26"/>
+      <c r="F71" s="26"/>
+      <c r="G71" s="26"/>
+      <c r="H71" s="26"/>
+      <c r="I71" s="26"/>
+      <c r="J71" s="26"/>
+    </row>
+    <row r="72" spans="1:10" ht="76.5">
+      <c r="A72" s="4">
+        <v>23</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="I72" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="J72" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="30.75">
+      <c r="F73" s="4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74" s="26"/>
+      <c r="B74" s="26"/>
+      <c r="C74" s="26"/>
+      <c r="D74" s="26"/>
+      <c r="E74" s="26"/>
+      <c r="F74" s="26"/>
+      <c r="G74" s="26"/>
+      <c r="H74" s="26"/>
+      <c r="I74" s="26"/>
+      <c r="J74" s="26"/>
+    </row>
+    <row r="75" spans="1:10" ht="30.75">
+      <c r="A75" s="4">
+        <v>24</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="F76" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="45.75">
+      <c r="F77" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H77" s="14" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="30.75">
+      <c r="F78" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
+      <c r="B79" s="26"/>
+      <c r="C79" s="26"/>
+      <c r="D79" s="26"/>
+      <c r="E79" s="26"/>
+      <c r="F79" s="26"/>
+      <c r="G79" s="26"/>
+      <c r="H79" s="26"/>
+      <c r="I79" s="26"/>
+      <c r="J79" s="26"/>
+    </row>
+    <row r="80" spans="1:10" ht="30.75">
+      <c r="A80" s="21">
+        <v>24</v>
+      </c>
+      <c r="B80" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="C80" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="D80" s="21"/>
+      <c r="E80" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F80" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G80" s="21"/>
+      <c r="H80" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="I80" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="J80" s="21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="30.75">
+      <c r="A81" s="21">
+        <v>25</v>
+      </c>
+      <c r="B81" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="C81" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="D81" s="21"/>
+      <c r="E81" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F81" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G81" s="21"/>
+      <c r="H81" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="I81" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="J81" s="21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="30.75">
+      <c r="A82" s="28">
+        <v>27</v>
+      </c>
+      <c r="B82" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D82" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="E82" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="F82" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="G82" s="28"/>
+      <c r="H82" s="28"/>
+      <c r="I82" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="J82" s="28" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10">
+      <c r="A83" s="29"/>
+      <c r="B83" s="29"/>
+      <c r="C83" s="26"/>
+      <c r="D83" s="29"/>
+      <c r="E83" s="29"/>
+      <c r="F83" s="29"/>
+      <c r="G83" s="29"/>
+      <c r="H83" s="29"/>
+      <c r="I83" s="29"/>
+      <c r="J83" s="29"/>
+    </row>
+    <row r="84" spans="1:10" ht="30.75">
+      <c r="A84" s="28">
+        <v>28</v>
+      </c>
+      <c r="B84" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D84" s="28"/>
+      <c r="E84" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="F84" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="G84" s="28"/>
+      <c r="H84" s="28"/>
+      <c r="I84" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="J84" s="28" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="A85" s="29"/>
+      <c r="B85" s="29"/>
+      <c r="C85" s="26"/>
+      <c r="D85" s="29"/>
+      <c r="E85" s="29"/>
+      <c r="F85" s="29"/>
+      <c r="G85" s="29"/>
+      <c r="H85" s="29"/>
+      <c r="I85" s="29"/>
+      <c r="J85" s="29"/>
+    </row>
+    <row r="86" spans="1:10" ht="30.75">
+      <c r="A86" s="28">
+        <v>29</v>
+      </c>
+      <c r="B86" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D86" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="E86" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="F86" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="G86" s="28"/>
+      <c r="H86" s="28"/>
+      <c r="I86" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="J86" s="28" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
+      <c r="A87" s="29"/>
+      <c r="B87" s="29"/>
+      <c r="C87" s="26"/>
+      <c r="D87" s="29"/>
+      <c r="E87" s="29"/>
+      <c r="F87" s="29"/>
+      <c r="G87" s="29"/>
+      <c r="H87" s="29"/>
+      <c r="I87" s="29"/>
+      <c r="J87" s="29"/>
+    </row>
+    <row r="88" spans="1:10" ht="30.75">
+      <c r="A88" s="28">
+        <v>30</v>
+      </c>
+      <c r="B88" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D88" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="E88" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="F88" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="G88" s="28"/>
+      <c r="H88" s="28"/>
+      <c r="I88" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="J88" s="28" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10">
+      <c r="A89" s="26"/>
+      <c r="B89" s="26"/>
+      <c r="C89" s="26"/>
+      <c r="D89" s="26"/>
+      <c r="E89" s="26"/>
+      <c r="F89" s="26"/>
+      <c r="G89" s="26"/>
+      <c r="H89" s="26"/>
+      <c r="I89" s="26"/>
+      <c r="J89" s="26"/>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="5"/>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="5"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G89" xr:uid="{C1301507-ED74-4DAD-9E09-2B817234A532}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="90" verticalDpi="90" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60332FED-4A7D-44D0-954A-5E76A8D8379A}">
+  <dimension ref="A1:G52"/>
+  <sheetFormatPr defaultColWidth="64.75" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="2.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.25" style="8" customWidth="1"/>
+    <col min="3" max="3" width="24" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.75" style="7" customWidth="1"/>
+    <col min="6" max="6" width="27.25" style="7" customWidth="1"/>
+    <col min="7" max="7" width="61.5" style="7" customWidth="1"/>
+    <col min="8" max="16384" width="64.75" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="16.5">
+      <c r="A1" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="16.5">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="C2" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="D2" s="32" t="s">
+        <v>164</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>165</v>
+      </c>
+      <c r="F2" s="32" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="16.5">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="C3" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="16.5">
+      <c r="A4" s="7">
+        <v>3</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>172</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>173</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.75">
+      <c r="B5" s="31"/>
+      <c r="C5" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+    </row>
+    <row r="6" spans="1:7" ht="16.5">
+      <c r="A6" s="7">
+        <v>4</v>
+      </c>
+      <c r="B6" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>177</v>
+      </c>
+      <c r="E6" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="F6" s="32" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="16.5">
+      <c r="A7" s="7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>179</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>177</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="16.5">
+      <c r="A8" s="7">
+        <v>6</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="E8" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="F8" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="G8" s="33"/>
+    </row>
+    <row r="9" spans="1:7" ht="16.5">
+      <c r="A9" s="7">
+        <v>7</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="C9" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>177</v>
+      </c>
+      <c r="E9" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="F9" s="32" t="s">
+        <v>185</v>
+      </c>
+      <c r="G9" s="33"/>
+    </row>
+    <row r="10" spans="1:7" ht="15.75">
+      <c r="A10" s="7">
+        <v>8</v>
+      </c>
+      <c r="B10" s="31"/>
+      <c r="C10" s="32" t="s">
+        <v>186</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="E10" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F10" s="32" t="s">
+        <v>188</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.75">
+      <c r="A11" s="7">
+        <v>9</v>
+      </c>
+      <c r="B11" s="31"/>
+      <c r="C11" s="32" t="s">
+        <v>190</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="E11" s="32" t="s">
+        <v>191</v>
+      </c>
+      <c r="F11" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.75">
+      <c r="A12" s="7">
+        <v>10</v>
+      </c>
+      <c r="B12" s="31"/>
+      <c r="C12" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="E12" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="F12" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="G12" s="36"/>
+    </row>
+    <row r="13" spans="1:7" ht="15.75">
+      <c r="A13" s="7">
+        <v>11</v>
+      </c>
+      <c r="B13" s="31"/>
+      <c r="C13" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="E13" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F13" s="32" t="s">
+        <v>198</v>
+      </c>
+      <c r="G13" s="36"/>
+    </row>
+    <row r="14" spans="1:7" ht="15.75">
+      <c r="A14" s="7">
+        <v>12</v>
+      </c>
+      <c r="B14" s="31"/>
+      <c r="C14" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="D14" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="E14" s="32" t="s">
+        <v>200</v>
+      </c>
+      <c r="F14" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="G14" s="36"/>
+    </row>
+    <row r="15" spans="1:7" ht="16.5">
+      <c r="A15" s="7">
+        <v>13</v>
+      </c>
+      <c r="B15" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>201</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="E15" s="32" t="s">
+        <v>202</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>203</v>
+      </c>
+      <c r="G15" s="37" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="16.5">
+      <c r="A16" s="7">
+        <v>14</v>
+      </c>
+      <c r="B16" s="31" t="s">
+        <v>205</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>206</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="E16" s="32" t="s">
+        <v>207</v>
+      </c>
+      <c r="F16" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="G16" s="37"/>
+    </row>
+    <row r="17" spans="1:7" ht="16.5">
+      <c r="A17" s="7">
+        <v>15</v>
+      </c>
+      <c r="B17" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>208</v>
+      </c>
+      <c r="D17" s="32" t="s">
+        <v>209</v>
+      </c>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="G17" s="14"/>
+    </row>
+    <row r="18" spans="1:7" ht="16.5">
+      <c r="A18" s="7">
+        <v>16</v>
+      </c>
+      <c r="B18" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="C18" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="D18" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="E18" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="F18" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="G18" s="37"/>
+    </row>
+    <row r="19" spans="1:7" ht="16.5">
+      <c r="A19" s="7">
+        <v>17</v>
+      </c>
+      <c r="B19" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="C19" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="D19" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="E19" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="F19" s="32" t="s">
+        <v>215</v>
+      </c>
+      <c r="G19" s="37" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="16.5">
+      <c r="A20" s="7">
+        <v>18</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>217</v>
+      </c>
+      <c r="C20" s="32" t="s">
+        <v>218</v>
+      </c>
+      <c r="D20" s="32" t="s">
+        <v>164</v>
+      </c>
+      <c r="E20" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F20" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="30.75">
+      <c r="A21" s="7">
+        <v>19</v>
+      </c>
+      <c r="B21" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="C21" s="32" t="s">
+        <v>220</v>
+      </c>
+      <c r="D21" s="34" t="s">
+        <v>164</v>
+      </c>
+      <c r="E21" s="34" t="s">
+        <v>221</v>
+      </c>
+      <c r="F21" s="32" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="16.5">
+      <c r="A22" s="7">
+        <v>20</v>
+      </c>
+      <c r="B22" s="31" t="s">
+        <v>223</v>
+      </c>
+      <c r="C22" s="32" t="s">
+        <v>224</v>
+      </c>
+      <c r="D22" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="E22" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F22" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="G22" s="14"/>
+    </row>
+    <row r="23" spans="1:7" ht="16.5">
+      <c r="A23" s="7">
+        <v>21</v>
+      </c>
+      <c r="B23" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="C23" s="32" t="s">
+        <v>225</v>
+      </c>
+      <c r="D23" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="E23" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F23" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="G23" s="14"/>
+    </row>
+    <row r="24" spans="1:7" ht="30.75">
+      <c r="A24" s="7">
+        <v>22</v>
+      </c>
+      <c r="B24" s="31" t="s">
+        <v>226</v>
+      </c>
+      <c r="C24" s="32" t="s">
+        <v>227</v>
+      </c>
+      <c r="D24" s="34" t="s">
+        <v>164</v>
+      </c>
+      <c r="E24" s="35" t="s">
+        <v>228</v>
+      </c>
+      <c r="F24" s="32" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7"/>
+    <row r="29" spans="1:7">
+      <c r="G29" s="1"/>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="G30" s="1"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="G31" s="1"/>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="G32" s="1"/>
+    </row>
+    <row r="33" spans="7:7">
+      <c r="G33" s="1"/>
+    </row>
+    <row r="34" spans="7:7">
+      <c r="G34" s="1"/>
+    </row>
+    <row r="35" spans="7:7">
+      <c r="G35" s="1"/>
+    </row>
+    <row r="36" spans="7:7">
+      <c r="G36" s="1"/>
+    </row>
+    <row r="37" spans="7:7">
+      <c r="G37" s="1"/>
+    </row>
+    <row r="38" spans="7:7">
+      <c r="G38" s="1"/>
+    </row>
+    <row r="47" spans="7:7">
+      <c r="G47" s="1"/>
+    </row>
+    <row r="48" spans="7:7">
+      <c r="G48" s="1"/>
+    </row>
+    <row r="49" spans="7:7">
+      <c r="G49" s="1"/>
+    </row>
+    <row r="50" spans="7:7">
+      <c r="G50" s="1"/>
+    </row>
+    <row r="51" spans="7:7">
+      <c r="G51" s="1"/>
+    </row>
+    <row r="52" spans="7:7">
+      <c r="G52" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1301507-ED74-4DAD-9E09-2B817234A532}">
   <dimension ref="A1:J107"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="2.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="21.875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="75.125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="24.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="53.375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="30.125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="46.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="58.375" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="8.625" style="3"/>
+    <col min="1" max="1" width="8" style="3" customWidth="1"/>
+    <col min="2" max="2" width="22.25" style="3" customWidth="1"/>
+    <col min="3" max="3" width="21.75" style="3" customWidth="1"/>
+    <col min="4" max="4" width="75.25" style="3" customWidth="1"/>
+    <col min="5" max="5" width="24.5" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.25" style="3" customWidth="1"/>
+    <col min="7" max="7" width="34.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="53.25" style="3" customWidth="1"/>
+    <col min="9" max="9" width="30.25" style="3" customWidth="1"/>
+    <col min="10" max="10" width="46.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="58.25" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="8.75" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.95">
+    <row r="1" spans="1:10" ht="15.6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1159,25 +3582,25 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="48">
+      <c r="J1" s="16" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="43.5">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -1194,789 +3617,817 @@
         <v>10</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="3" t="s">
+    </row>
+    <row r="3" spans="1:10" ht="29.1">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="32.1">
-      <c r="A3" s="14">
-        <v>2</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="14" t="s">
+      <c r="G3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="14" t="s">
+      <c r="I3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" s="14" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="48">
+    </row>
+    <row r="4" spans="1:10" ht="72.599999999999994">
       <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="159.94999999999999">
+      <c r="J4" s="4" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="144.94999999999999">
       <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>30</v>
+        <v>232</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="43.5">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I6" s="4"/>
+    </row>
+    <row r="7" spans="1:10" ht="72.599999999999994">
+      <c r="A7" s="13">
+        <v>6</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="48">
-      <c r="A6" s="14">
-        <v>5</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="32.1">
-      <c r="A7" s="14">
-        <v>6</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="32.1">
+      <c r="H7" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="29.1">
       <c r="A8" s="4">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="H8" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="32.1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="29.1">
       <c r="A9" s="4">
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="F9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="H9" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="32.1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="29.1">
       <c r="A10" s="4">
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="F10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="H10" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="48">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="29.1">
       <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="H11" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="159.94999999999999">
+        <v>19</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="144.94999999999999">
       <c r="A12" s="4">
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>59</v>
+        <v>239</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>62</v>
+        <v>240</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>63</v>
+        <v>241</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="32.1">
+        <v>242</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="72.599999999999994">
       <c r="A13" s="4">
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="F13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="H13" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="32.1">
+        <v>19</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="29.1">
       <c r="A14" s="4">
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="F14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="29.1">
+      <c r="A15" s="4">
         <v>14</v>
       </c>
-      <c r="H14" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="32.1">
-      <c r="A15" s="14">
-        <v>14</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="F15" s="14" t="s">
+      <c r="B15" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G15" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="I15" s="14"/>
+      <c r="H15" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15" s="4"/>
       <c r="J15" s="14" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="32.1">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="29.1">
       <c r="A16" s="3">
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="F16" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="H16" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="32.1">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="29.1">
       <c r="A17" s="3">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>79</v>
+        <v>94</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>109</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="F17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="H17" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="32.1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="29.1">
       <c r="A18" s="3">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="F18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="H18" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="32.1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="29.1">
       <c r="A19" s="3">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="F19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="H19" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="32.1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="29.1">
       <c r="A20" s="3">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="F20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="H20" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="32.1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="29.1">
       <c r="A21" s="3">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="F21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="H21" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="32.1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="29.1">
       <c r="A22" s="3">
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="32.1">
+        <v>19</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="29.1">
       <c r="A23" s="3">
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>93</v>
+        <v>130</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="F23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="H23" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="32.1">
+        <v>19</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="116.1">
       <c r="A24" s="3">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>66</v>
-      </c>
       <c r="D24" s="4" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="F24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="H24" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="32.1">
-      <c r="A25" s="3">
+        <v>19</v>
+      </c>
+      <c r="J24" s="15" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="29.1">
+      <c r="A25" s="20">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F25" s="3" t="s">
+      <c r="B25" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="32.1">
-      <c r="A26" s="3">
+      <c r="H25" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="I25" s="20"/>
+      <c r="J25" s="22" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="29.1">
+      <c r="A26" s="20">
         <v>25</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F26" s="3" t="s">
+      <c r="B26" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="32.1">
+      <c r="H26" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="I26" s="20"/>
+      <c r="J26" s="22" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="57.95">
       <c r="A27" s="3">
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="F27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="29.1">
+      <c r="A28" s="10">
+        <v>27</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="G28" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="32.1">
-      <c r="A28" s="11">
-        <v>27</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="F28" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="G28" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-    </row>
-    <row r="29" spans="1:10" ht="32.1">
-      <c r="A29" s="11">
+      <c r="H28" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
+    </row>
+    <row r="29" spans="1:10" ht="29.1">
+      <c r="A29" s="10">
         <v>28</v>
       </c>
-      <c r="B29" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="F29" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="G29" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-    </row>
-    <row r="30" spans="1:10" ht="32.1">
-      <c r="A30" s="11">
+      <c r="B29" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+    </row>
+    <row r="30" spans="1:10" ht="29.1">
+      <c r="A30" s="10">
         <v>29</v>
       </c>
-      <c r="B30" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="F30" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="G30" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-    </row>
-    <row r="31" spans="1:10" ht="32.1">
-      <c r="A31" s="11">
+      <c r="B30" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+    </row>
+    <row r="31" spans="1:10" ht="29.1">
+      <c r="A31" s="10">
         <v>30</v>
       </c>
-      <c r="B31" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="F31" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="G31" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13"/>
+      <c r="B31" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="5"/>
@@ -2154,572 +4605,508 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60332FED-4A7D-44D0-954A-5E76A8D8379A}">
-  <dimension ref="A1:H51"/>
-  <sheetFormatPr defaultColWidth="64.625" defaultRowHeight="15"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{290699D1-F346-43C3-B46C-B1515ED0A8AC}">
+  <dimension ref="A1:H32"/>
+  <sheetFormatPr defaultColWidth="43.625" defaultRowHeight="14.1"/>
   <cols>
-    <col min="1" max="1" width="2.875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.125" style="9" customWidth="1"/>
-    <col min="3" max="3" width="24" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="64.625" style="8" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="34.875" style="8" customWidth="1"/>
-    <col min="7" max="7" width="27.125" style="8" customWidth="1"/>
-    <col min="8" max="8" width="61.5" style="8" customWidth="1"/>
-    <col min="9" max="16384" width="64.625" style="8"/>
+    <col min="1" max="1" width="2.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.625" customWidth="1"/>
+    <col min="3" max="3" width="24.625" customWidth="1"/>
+    <col min="4" max="4" width="42.375" customWidth="1"/>
+    <col min="5" max="5" width="32.125" customWidth="1"/>
+    <col min="6" max="6" width="43.25" style="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="54.75" customWidth="1"/>
+    <col min="8" max="8" width="42.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.100000000000001">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="17.100000000000001">
-      <c r="A2" s="8">
+    <row r="1" spans="1:8" ht="15.6">
+      <c r="A1" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="G2" s="7" t="s">
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="43.5">
+      <c r="A2" s="3">
+        <v>3</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3" spans="1:8" ht="14.45">
+      <c r="A3" s="3"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" spans="1:8" ht="29.1">
+      <c r="A4" s="3"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" spans="1:8" ht="57.95">
+      <c r="A5" s="3"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="29.1">
+      <c r="A6" s="3"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="14.45">
+      <c r="A7" s="18"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+    </row>
+    <row r="8" spans="1:8" ht="43.5">
+      <c r="A8" s="3">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" spans="1:8" ht="29.1">
+      <c r="A9" s="3"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:8" ht="43.5">
+      <c r="A10" s="3"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="43.5">
+      <c r="A11" s="3"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="40.5" customHeight="1">
+      <c r="A12" s="3"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" ht="42" customHeight="1">
+      <c r="A13" s="3"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" spans="1:8" ht="39" customHeight="1">
+      <c r="A14" s="3"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15" spans="1:8" ht="48" customHeight="1">
+      <c r="A15" s="3"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="H15" s="4"/>
+    </row>
+    <row r="16" spans="1:8" ht="14.45">
+      <c r="A16" s="18"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+    </row>
+    <row r="17" spans="1:8" ht="43.5">
+      <c r="A17" s="4">
+        <v>5</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="H17" s="4"/>
+    </row>
+    <row r="18" spans="1:8" ht="14.45">
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+    </row>
+    <row r="19" spans="1:8" ht="43.5">
+      <c r="A19" s="4">
+        <v>11</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+    </row>
+    <row r="20" spans="1:8" ht="14.45">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+    </row>
+    <row r="21" spans="1:8" ht="29.1">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="4" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="17.100000000000001">
-      <c r="A3" s="8">
-        <v>2</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="C3" s="7" t="s">
+      <c r="G21" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="H21" s="4"/>
+    </row>
+    <row r="22" spans="1:8" ht="72.599999999999994">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="29.1">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H23" s="4"/>
+    </row>
+    <row r="24" spans="1:8" ht="29.1">
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+    </row>
+    <row r="25" spans="1:8" ht="14.45">
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+    </row>
+    <row r="26" spans="1:8" ht="29.1">
+      <c r="A26" s="3">
+        <v>21</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7" t="s">
+      <c r="C26" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G26" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="17.100000000000001">
-      <c r="A4" s="8">
-        <v>3</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7" t="s">
+      <c r="H26" s="4"/>
+    </row>
+    <row r="27" spans="1:8" ht="29.1">
+      <c r="A27" s="3"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H27" s="4"/>
+    </row>
+    <row r="28" spans="1:8" ht="43.5">
+      <c r="A28" s="3"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G28" s="3"/>
+      <c r="H28" s="4"/>
+    </row>
+    <row r="29" spans="1:8" ht="29.1">
+      <c r="A29" s="3"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="4" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="17.100000000000001">
-      <c r="A5" s="8">
-        <v>4</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="C5" s="7" t="s">
+      <c r="G29" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="H29" s="4"/>
+    </row>
+    <row r="30" spans="1:8" ht="29.1">
+      <c r="A30" s="3"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="17.100000000000001">
-      <c r="A6" s="8">
-        <v>5</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="17.100000000000001">
-      <c r="A7" s="8">
-        <v>6</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="H7" s="15"/>
-    </row>
-    <row r="8" spans="1:8" ht="17.100000000000001">
-      <c r="A8" s="8">
-        <v>7</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="H8" s="15"/>
-    </row>
-    <row r="9" spans="1:8" ht="15.95">
-      <c r="A9" s="8">
-        <v>8</v>
-      </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14" t="s">
+      <c r="G30" s="3"/>
+      <c r="H30" s="4"/>
+    </row>
+    <row r="31" spans="1:8" ht="14.45">
+      <c r="A31" s="18"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="19"/>
+    </row>
+    <row r="32" spans="1:8" ht="87">
+      <c r="A32" s="3">
+        <v>26</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="G9" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="H9" s="14" t="s">
+      <c r="C32" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="G32" s="4" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="15.95">
-      <c r="A10" s="8">
-        <v>9</v>
-      </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="15.95">
-      <c r="A11" s="8">
-        <v>10</v>
-      </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="H11" s="15"/>
-    </row>
-    <row r="12" spans="1:8" ht="15.95">
-      <c r="A12" s="8">
-        <v>11</v>
-      </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="H12" s="15"/>
-    </row>
-    <row r="13" spans="1:8" ht="15.95">
-      <c r="A13" s="8">
-        <v>12</v>
-      </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="H13" s="15"/>
-    </row>
-    <row r="14" spans="1:8" ht="17.100000000000001">
-      <c r="A14" s="8">
-        <v>13</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="H14" s="14" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="17.100000000000001">
-      <c r="A15" s="8">
-        <v>14</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="17.100000000000001">
-      <c r="A16" s="8">
-        <v>15</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="17.100000000000001">
-      <c r="A17" s="8">
-        <v>16</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="17.100000000000001">
-      <c r="A18" s="8">
-        <v>17</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="G18" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="H18" s="14" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="17.100000000000001">
-      <c r="A19" s="8">
-        <v>18</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="G19" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="H19" s="14" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="32.1">
-      <c r="A20" s="8">
-        <v>19</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="17.100000000000001">
-      <c r="A21" s="8">
-        <v>20</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="H21" s="14" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="17.100000000000001">
-      <c r="A22" s="8">
-        <v>21</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="H22" s="14" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="32.1">
-      <c r="A23" s="8">
-        <v>22</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="F23" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="H28" s="1"/>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="H29" s="1"/>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="H30" s="1"/>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="H31" s="1"/>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="H32" s="1"/>
-    </row>
-    <row r="33" spans="8:8">
-      <c r="H33" s="1"/>
-    </row>
-    <row r="34" spans="8:8">
-      <c r="H34" s="1"/>
-    </row>
-    <row r="35" spans="8:8">
-      <c r="H35" s="1"/>
-    </row>
-    <row r="36" spans="8:8">
-      <c r="H36" s="1"/>
-    </row>
-    <row r="37" spans="8:8">
-      <c r="H37" s="1"/>
-    </row>
-    <row r="46" spans="8:8">
-      <c r="H46" s="1"/>
-    </row>
-    <row r="47" spans="8:8">
-      <c r="H47" s="1"/>
-    </row>
-    <row r="48" spans="8:8">
-      <c r="H48" s="1"/>
-    </row>
-    <row r="49" spans="8:8">
-      <c r="H49" s="1"/>
-    </row>
-    <row r="50" spans="8:8">
-      <c r="H50" s="1"/>
-    </row>
-    <row r="51" spans="8:8">
-      <c r="H51" s="1"/>
+      <c r="H32" s="4" t="s">
+        <v>266</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2777,64 +5164,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Project xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56" xsi:nil="true"/>
-    <TaxCatchAll xmlns="247916fd-1a60-495e-a02f-9dbb51413255" xsi:nil="true"/>
-    <PID xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56" xsi:nil="true"/>
-    <ProjectStartDate xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56" xsi:nil="true"/>
-    <ProjectEndDate xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56" xsi:nil="true"/>
-    <Status xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56">Active</Status>
-    <Function xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56">DVC Education - Student and Scholarly Services</Function>
-    <DocumentSetDescription xmlns="http://schemas.microsoft.com/sharepoint/v3">Creating, managing and retrieving assets and their associated metadata and rights/permissions details is a significant endeavour for the University with over 100K assets under various management regimes and between 10,000 to 20,000 high important assets digitised each year (Source: 2021 DAM analysis).  
-Currently each collection is independently and sparsely digitised. This leads to inconsistency in the housing, finding and accessing these assets. This creates a security and compliance risk as well as inefficiencies. We have no way of measuring performance of these assets, systematically managing rights, maximising consistency and re-use.
-In SmartSheet PID254 has been closed and replaced with PID365. </DocumentSetDescription>
-    <LinktoCanvas xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56" xsi:nil="true"/>
-    <Members xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Members>
-    <Deliverable xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56" xsi:nil="true"/>
-    <LeadTeam xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56">Digital</LeadTeam>
-    <LinktoCloseReport xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </LinktoCloseReport>
-    <ProjectLead xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56">
-      <UserInfo>
-        <DisplayName>Shona Barrett</DisplayName>
-        <AccountId>1453</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </ProjectLead>
-    <ToolsUsed xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56" xsi:nil="true"/>
-    <LinktoStrategy xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56" xsi:nil="true"/>
-    <OtherGroups xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56" xsi:nil="true"/>
-    <Pillar xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56">Digital Transformation</Pillar>
-    <LessonsLearned xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_dlc_DocId xmlns="247916fd-1a60-495e-a02f-9dbb51413255">AMZWAK7HTCT4-1043692212-59917</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="247916fd-1a60-495e-a02f-9dbb51413255">
-      <Url>https://unimelbcloud.sharepoint.com/sites/OPGProjects/_layouts/15/DocIdRedir.aspx?ID=AMZWAK7HTCT4-1043692212-59917</Url>
-      <Description>AMZWAK7HTCT4-1043692212-59917</Description>
-    </_dlc_DocIdUrl>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100107669A72ECB114D9FF76A8CA171E054" ma:contentTypeVersion="46" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="10f9caf407deae0f3f217c6265eabac5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="7c1ec1a7-62a1-4012-8155-c336c8cfdc56" xmlns:ns3="247916fd-1a60-495e-a02f-9dbb51413255" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2de188e63c5f14f3bb9c9b41488d10c7" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -3331,12 +5660,70 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Project xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56" xsi:nil="true"/>
+    <TaxCatchAll xmlns="247916fd-1a60-495e-a02f-9dbb51413255" xsi:nil="true"/>
+    <PID xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56" xsi:nil="true"/>
+    <ProjectStartDate xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56" xsi:nil="true"/>
+    <ProjectEndDate xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56" xsi:nil="true"/>
+    <Status xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56">Active</Status>
+    <Function xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56">DVC Education - Student and Scholarly Services</Function>
+    <DocumentSetDescription xmlns="http://schemas.microsoft.com/sharepoint/v3">Creating, managing and retrieving assets and their associated metadata and rights/permissions details is a significant endeavour for the University with over 100K assets under various management regimes and between 10,000 to 20,000 high important assets digitised each year (Source: 2021 DAM analysis).  
+Currently each collection is independently and sparsely digitised. This leads to inconsistency in the housing, finding and accessing these assets. This creates a security and compliance risk as well as inefficiencies. We have no way of measuring performance of these assets, systematically managing rights, maximising consistency and re-use.
+In SmartSheet PID254 has been closed and replaced with PID365. </DocumentSetDescription>
+    <LinktoCanvas xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56" xsi:nil="true"/>
+    <Members xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Members>
+    <Deliverable xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56" xsi:nil="true"/>
+    <LeadTeam xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56">Digital</LeadTeam>
+    <LinktoCloseReport xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </LinktoCloseReport>
+    <ProjectLead xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56">
+      <UserInfo>
+        <DisplayName>Shona Barrett</DisplayName>
+        <AccountId>1453</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </ProjectLead>
+    <ToolsUsed xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56" xsi:nil="true"/>
+    <LinktoStrategy xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56" xsi:nil="true"/>
+    <OtherGroups xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56" xsi:nil="true"/>
+    <Pillar xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56">Digital Transformation</Pillar>
+    <LessonsLearned xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c1ec1a7-62a1-4012-8155-c336c8cfdc56">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_dlc_DocId xmlns="247916fd-1a60-495e-a02f-9dbb51413255">AMZWAK7HTCT4-1043692212-61969</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="247916fd-1a60-495e-a02f-9dbb51413255">
+      <Url>https://unimelbcloud.sharepoint.com/sites/OPGProjects/_layouts/15/DocIdRedir.aspx?ID=AMZWAK7HTCT4-1043692212-61969</Url>
+      <Description>AMZWAK7HTCT4-1043692212-61969</Description>
+    </_dlc_DocIdUrl>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A02A138A-A9A0-4A5C-AD13-5146096A96E8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F96701C4-2080-4DFE-BE16-91280081C66E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{840A8891-0277-4453-B154-09C236A91E67}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3344,5 +5731,5 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{840A8891-0277-4453-B154-09C236A91E67}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F96701C4-2080-4DFE-BE16-91280081C66E}"/>
 </file>